--- a/research/traditional_assets/database/data/norway/norway_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_hotel_gaming.xlsx
@@ -587,17 +587,32 @@
           <t>Hotel/Gaming</t>
         </is>
       </c>
+      <c r="G2">
+        <v>-0.5296610169491525</v>
+      </c>
+      <c r="H2">
+        <v>-0.5296610169491525</v>
+      </c>
+      <c r="I2">
+        <v>-0.9202118644067796</v>
+      </c>
+      <c r="J2">
+        <v>-0.9202118644067796</v>
+      </c>
       <c r="K2">
-        <v>-6.720000000000001</v>
+        <v>-33.805</v>
+      </c>
+      <c r="L2">
+        <v>-1.432415254237288</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.056</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.0006542820422946606</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.001656559680520633</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -609,64 +624,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.056</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>41.8</v>
+        <v>5.89</v>
       </c>
       <c r="V2">
-        <v>0.3046869305342955</v>
+        <v>0.06881645051992054</v>
+      </c>
+      <c r="W2">
+        <v>-0.1520580412398283</v>
       </c>
       <c r="X2">
-        <v>0.09231748257915369</v>
+        <v>0.1681767257093608</v>
+      </c>
+      <c r="Y2">
+        <v>-0.3202347669491891</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>0.08111916955968791</v>
+      </c>
+      <c r="AA2">
+        <v>-0.04707971232626838</v>
       </c>
       <c r="AB2">
-        <v>0.05290273542556156</v>
+        <v>0.08122448494631136</v>
+      </c>
+      <c r="AC2">
+        <v>-0.1283041972725797</v>
       </c>
       <c r="AD2">
-        <v>200.43</v>
+        <v>257.72</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>200.43</v>
+        <v>257.72</v>
       </c>
       <c r="AG2">
-        <v>158.63</v>
+        <v>251.83</v>
       </c>
       <c r="AH2">
-        <v>0.5936555891238671</v>
+        <v>0.7506917945879816</v>
       </c>
       <c r="AI2">
-        <v>0.5939898645645023</v>
+        <v>0.7773889961389961</v>
       </c>
       <c r="AJ2">
-        <v>0.5362382529916842</v>
+        <v>0.7463398731551182</v>
       </c>
       <c r="AK2">
-        <v>0.5365828907756317</v>
+        <v>0.7733624051837975</v>
       </c>
       <c r="AL2">
-        <v>1.092</v>
+        <v>6.73</v>
       </c>
       <c r="AM2">
-        <v>-0.6699999999999999</v>
+        <v>6.351000000000001</v>
       </c>
       <c r="AN2">
-        <v>-21.16473072861668</v>
+        <v>-14.98372093023256</v>
       </c>
       <c r="AO2">
-        <v>-9.571428571428571</v>
+        <v>-3.226894502228826</v>
       </c>
       <c r="AP2">
-        <v>-16.75079197465681</v>
+        <v>-14.64127906976744</v>
       </c>
       <c r="AQ2">
-        <v>15.6</v>
+        <v>-3.419461502125649</v>
       </c>
     </row>
     <row r="3">
@@ -686,16 +716,16 @@
         </is>
       </c>
       <c r="K3">
-        <v>-1.73</v>
+        <v>-0.305</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.056</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01651917404129793</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.1836065573770492</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -707,7 +737,10 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.056</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -716,61 +749,58 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>-0.2032902467685077</v>
+        <v>-0.02401574803149606</v>
       </c>
       <c r="X3">
-        <v>0.08764483051835883</v>
+        <v>0.1475421364998342</v>
       </c>
       <c r="Y3">
-        <v>-0.2909350772868665</v>
+        <v>-0.1715578845313303</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.05613207547169811</v>
+        <v>-0.01472364143056201</v>
       </c>
       <c r="AB3">
-        <v>0.05224257461033864</v>
+        <v>0.08136234013742924</v>
       </c>
       <c r="AC3">
-        <v>-0.1083746500820368</v>
+        <v>-0.09608598156799125</v>
       </c>
       <c r="AD3">
-        <v>8.83</v>
+        <v>6.32</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>8.83</v>
+        <v>6.32</v>
       </c>
       <c r="AG3">
-        <v>8.83</v>
+        <v>6.32</v>
       </c>
       <c r="AH3">
-        <v>0.5377588306942752</v>
+        <v>0.650875386199794</v>
       </c>
       <c r="AI3">
-        <v>0.3366374380480366</v>
+        <v>0.3288241415192508</v>
       </c>
       <c r="AJ3">
-        <v>0.5377588306942752</v>
+        <v>0.650875386199794</v>
       </c>
       <c r="AK3">
-        <v>0.3366374380480366</v>
+        <v>0.3288241415192508</v>
       </c>
       <c r="AL3">
-        <v>0.235</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.233</v>
-      </c>
-      <c r="AO3">
-        <v>-4.051063829787234</v>
+        <v>-0.095</v>
       </c>
       <c r="AQ3">
-        <v>-4.085836909871245</v>
+        <v>3.336842105263158</v>
       </c>
     </row>
     <row r="4">
@@ -789,8 +819,23 @@
           <t>Hotel/Gaming</t>
         </is>
       </c>
+      <c r="G4">
+        <v>-0.5296610169491525</v>
+      </c>
+      <c r="H4">
+        <v>-0.5296610169491525</v>
+      </c>
+      <c r="I4">
+        <v>-0.9067796610169491</v>
+      </c>
+      <c r="J4">
+        <v>-0.9067796610169491</v>
+      </c>
       <c r="K4">
-        <v>-4.99</v>
+        <v>-33.5</v>
+      </c>
+      <c r="L4">
+        <v>-1.419491525423729</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -814,58 +859,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>41.8</v>
+        <v>5.89</v>
       </c>
       <c r="V4">
-        <v>0.3225308641975309</v>
+        <v>0.071654501216545</v>
+      </c>
+      <c r="W4">
+        <v>-0.2801003344481606</v>
       </c>
       <c r="X4">
-        <v>0.09699013463994854</v>
+        <v>0.1888113149188873</v>
+      </c>
+      <c r="Y4">
+        <v>-0.4689116493670479</v>
+      </c>
+      <c r="Z4">
+        <v>0.08760207869339273</v>
+      </c>
+      <c r="AA4">
+        <v>-0.07943578322197475</v>
       </c>
       <c r="AB4">
-        <v>0.05356289624078448</v>
+        <v>0.08108662975519348</v>
+      </c>
+      <c r="AC4">
+        <v>-0.1605224129771682</v>
       </c>
       <c r="AD4">
-        <v>191.6</v>
+        <v>251.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>191.6</v>
+        <v>251.4</v>
       </c>
       <c r="AG4">
-        <v>149.8</v>
+        <v>245.51</v>
       </c>
       <c r="AH4">
-        <v>0.5965130759651308</v>
+        <v>0.7535971223021583</v>
       </c>
       <c r="AI4">
-        <v>0.615681233933162</v>
+        <v>0.8049951969260326</v>
       </c>
       <c r="AJ4">
-        <v>0.5361488904795992</v>
+        <v>0.7491684721247445</v>
       </c>
       <c r="AK4">
-        <v>0.5560504825538234</v>
+        <v>0.8012466956039294</v>
       </c>
       <c r="AL4">
-        <v>0.857</v>
+        <v>6.73</v>
       </c>
       <c r="AM4">
-        <v>-0.903</v>
+        <v>6.446000000000001</v>
       </c>
       <c r="AN4">
-        <v>-20.23231256599789</v>
+        <v>-14.61627906976744</v>
       </c>
       <c r="AO4">
-        <v>-11.08518086347725</v>
+        <v>-3.179791976225854</v>
       </c>
       <c r="AP4">
-        <v>-15.81837381203801</v>
+        <v>-14.27383720930233</v>
       </c>
       <c r="AQ4">
-        <v>10.52048726467331</v>
+        <v>-3.319888302823456</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/norway/norway_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_hotel_gaming.xlsx
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.5296610169491525</v>
+        <v>-0.4523475387703622</v>
       </c>
       <c r="H2">
-        <v>-0.5296610169491525</v>
+        <v>-0.4523475387703622</v>
       </c>
       <c r="I2">
-        <v>-0.9202118644067796</v>
+        <v>-0.6233279448599292</v>
       </c>
       <c r="J2">
-        <v>-0.9202118644067796</v>
+        <v>-0.6233279448599292</v>
       </c>
       <c r="K2">
-        <v>-33.805</v>
+        <v>-90.51000000000001</v>
       </c>
       <c r="L2">
-        <v>-1.432415254237288</v>
+        <v>-1.607837564173165</v>
       </c>
       <c r="M2">
-        <v>0.056</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.0006542820422946606</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.001656559680520633</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,79 +624,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0.056</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>5.89</v>
+        <v>35.1</v>
       </c>
       <c r="V2">
-        <v>0.06881645051992054</v>
+        <v>0.5331915540027343</v>
       </c>
       <c r="W2">
-        <v>-0.1520580412398283</v>
+        <v>-0.7868194047745879</v>
       </c>
       <c r="X2">
-        <v>0.1681767257093608</v>
+        <v>0.1622861491417565</v>
       </c>
       <c r="Y2">
-        <v>-0.3202347669491891</v>
+        <v>-0.9491055539163443</v>
       </c>
       <c r="Z2">
-        <v>0.08111916955968791</v>
+        <v>0.1745844188065997</v>
       </c>
       <c r="AA2">
-        <v>-0.04707971232626838</v>
+        <v>-0.07466892110988577</v>
       </c>
       <c r="AB2">
-        <v>0.08122448494631136</v>
+        <v>0.06991543688134236</v>
       </c>
       <c r="AC2">
-        <v>-0.1283041972725797</v>
+        <v>-0.1445843579912281</v>
       </c>
       <c r="AD2">
-        <v>257.72</v>
+        <v>330.11</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>257.72</v>
+        <v>330.11</v>
       </c>
       <c r="AG2">
-        <v>251.83</v>
+        <v>295.01</v>
       </c>
       <c r="AH2">
-        <v>0.7506917945879816</v>
+        <v>0.8337374349648937</v>
       </c>
       <c r="AI2">
-        <v>0.7773889961389961</v>
+        <v>0.797347890147581</v>
       </c>
       <c r="AJ2">
-        <v>0.7463398731551182</v>
+        <v>0.81756457155526</v>
       </c>
       <c r="AK2">
-        <v>0.7733624051837975</v>
+        <v>0.7785753872951361</v>
       </c>
       <c r="AL2">
-        <v>6.73</v>
+        <v>38.404</v>
       </c>
       <c r="AM2">
-        <v>6.351000000000001</v>
+        <v>34.304</v>
       </c>
       <c r="AN2">
-        <v>-14.98372093023256</v>
+        <v>-13.04782608695652</v>
       </c>
       <c r="AO2">
-        <v>-3.226894502228826</v>
+        <v>-0.9136808665763981</v>
       </c>
       <c r="AP2">
-        <v>-14.64127906976744</v>
+        <v>-11.66047430830039</v>
       </c>
       <c r="AQ2">
-        <v>-3.419461502125649</v>
+        <v>-1.022883628731343</v>
       </c>
     </row>
     <row r="3">
@@ -715,17 +712,32 @@
           <t>Hotel/Gaming</t>
         </is>
       </c>
+      <c r="G3">
+        <v>-4.989247311827957</v>
+      </c>
+      <c r="H3">
+        <v>-4.989247311827957</v>
+      </c>
+      <c r="I3">
+        <v>-6.333333333333333</v>
+      </c>
+      <c r="J3">
+        <v>-6.333333333333333</v>
+      </c>
       <c r="K3">
-        <v>-0.305</v>
+        <v>-1.01</v>
+      </c>
+      <c r="L3">
+        <v>-10.86021505376344</v>
       </c>
       <c r="M3">
-        <v>0.056</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.01651917404129793</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.1836065573770492</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -737,10 +749,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0.056</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -749,58 +758,61 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>-0.02401574803149606</v>
+        <v>-0.1040164778578785</v>
       </c>
       <c r="X3">
-        <v>0.1475421364998342</v>
+        <v>0.1113031763315152</v>
       </c>
       <c r="Y3">
-        <v>-0.1715578845313303</v>
+        <v>-0.2153196541893936</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.005801621958827199</v>
       </c>
       <c r="AA3">
-        <v>-0.01472364143056201</v>
+        <v>-0.03674360573923893</v>
       </c>
       <c r="AB3">
-        <v>0.08136234013742924</v>
+        <v>0.07049898122368251</v>
       </c>
       <c r="AC3">
-        <v>-0.09608598156799125</v>
+        <v>-0.1072425869629214</v>
       </c>
       <c r="AD3">
-        <v>6.32</v>
+        <v>5.01</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.32</v>
+        <v>5.01</v>
       </c>
       <c r="AG3">
-        <v>6.32</v>
+        <v>5.01</v>
       </c>
       <c r="AH3">
-        <v>0.650875386199794</v>
+        <v>0.5866510538641686</v>
       </c>
       <c r="AI3">
-        <v>0.3288241415192508</v>
+        <v>0.2621664050235479</v>
       </c>
       <c r="AJ3">
-        <v>0.650875386199794</v>
+        <v>0.5866510538641686</v>
       </c>
       <c r="AK3">
-        <v>0.3288241415192508</v>
+        <v>0.2621664050235479</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.904</v>
       </c>
       <c r="AM3">
-        <v>-0.095</v>
+        <v>0.904</v>
+      </c>
+      <c r="AO3">
+        <v>-0.6515486725663716</v>
       </c>
       <c r="AQ3">
-        <v>3.336842105263158</v>
+        <v>-0.6515486725663716</v>
       </c>
     </row>
     <row r="4">
@@ -820,22 +832,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>-0.5296610169491525</v>
+        <v>-0.4448398576512455</v>
       </c>
       <c r="H4">
-        <v>-0.5296610169491525</v>
+        <v>-0.4448398576512455</v>
       </c>
       <c r="I4">
-        <v>-0.9067796610169491</v>
+        <v>-0.6138790035587188</v>
       </c>
       <c r="J4">
-        <v>-0.9067796610169491</v>
+        <v>-0.6138790035587188</v>
       </c>
       <c r="K4">
-        <v>-33.5</v>
+        <v>-89.5</v>
       </c>
       <c r="L4">
-        <v>-1.419491525423729</v>
+        <v>-1.592526690391459</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -859,73 +871,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>5.89</v>
+        <v>35.1</v>
       </c>
       <c r="V4">
-        <v>0.071654501216545</v>
+        <v>0.5634028892455859</v>
       </c>
       <c r="W4">
-        <v>-0.2801003344481606</v>
+        <v>-1.469622331691297</v>
       </c>
       <c r="X4">
-        <v>0.1888113149188873</v>
+        <v>0.2132691219519977</v>
       </c>
       <c r="Y4">
-        <v>-0.4689116493670479</v>
+        <v>-1.682891453643295</v>
       </c>
       <c r="Z4">
-        <v>0.08760207869339273</v>
+        <v>0.1834143794262589</v>
       </c>
       <c r="AA4">
-        <v>-0.07943578322197475</v>
+        <v>-0.1125942364805326</v>
       </c>
       <c r="AB4">
-        <v>0.08108662975519348</v>
+        <v>0.06933189253900221</v>
       </c>
       <c r="AC4">
-        <v>-0.1605224129771682</v>
+        <v>-0.1819261290195348</v>
       </c>
       <c r="AD4">
-        <v>251.4</v>
+        <v>325.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>251.4</v>
+        <v>325.1</v>
       </c>
       <c r="AG4">
-        <v>245.51</v>
+        <v>290</v>
       </c>
       <c r="AH4">
-        <v>0.7535971223021583</v>
+        <v>0.8391843056272587</v>
       </c>
       <c r="AI4">
-        <v>0.8049951969260326</v>
+        <v>0.8232463914915168</v>
       </c>
       <c r="AJ4">
-        <v>0.7491684721247445</v>
+        <v>0.8231620777746239</v>
       </c>
       <c r="AK4">
-        <v>0.8012466956039294</v>
+        <v>0.8060033351862146</v>
       </c>
       <c r="AL4">
-        <v>6.73</v>
+        <v>37.5</v>
       </c>
       <c r="AM4">
-        <v>6.446000000000001</v>
+        <v>33.4</v>
       </c>
       <c r="AN4">
-        <v>-14.61627906976744</v>
+        <v>-12.8498023715415</v>
       </c>
       <c r="AO4">
-        <v>-3.179791976225854</v>
+        <v>-0.92</v>
       </c>
       <c r="AP4">
-        <v>-14.27383720930233</v>
+        <v>-11.46245059288538</v>
       </c>
       <c r="AQ4">
-        <v>-3.319888302823456</v>
+        <v>-1.032934131736527</v>
       </c>
     </row>
   </sheetData>
